--- a/Audit_Exceptions_Report.xlsx
+++ b/Audit_Exceptions_Report.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -538,47 +538,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Missing SSN, Sanctions Issue: Pending</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Test User 4</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Savings</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Failed</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G4" s="1" t="n">
-        <v>46093</v>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Sanctions Issue: Failed</t>
+          <t>Missing SSN</t>
         </is>
       </c>
     </row>

--- a/Audit_Exceptions_Report.xlsx
+++ b/Audit_Exceptions_Report.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -538,7 +538,47 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Missing SSN</t>
+          <t>Missing SSN, Sanctions Issue: Pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Test User 4</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Savings</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Failed</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G4" s="1" t="n">
+        <v>46093</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Sanctions Issue: Failed</t>
         </is>
       </c>
     </row>
